--- a/data/s4/Aradas/archetypes/stats_trans.xlsx
+++ b/data/s4/Aradas/archetypes/stats_trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s4\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E0A74C-5391-4126-9DE9-C0DCE5FF8A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D522560-C4C5-4E8A-BF79-53BCA70D61DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -99,6 +99,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -130,12 +136,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,8 +495,8 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2">
-        <v>0.8</v>
+      <c r="C3" s="3">
+        <v>0.4</v>
       </c>
       <c r="D3" s="2">
         <v>0.1706</v>
@@ -528,8 +535,8 @@
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2">
-        <v>0.8</v>
+      <c r="C5" s="3">
+        <v>0.4</v>
       </c>
       <c r="D5" s="2">
         <v>0.2412</v>
@@ -568,8 +575,8 @@
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2">
-        <v>0.8</v>
+      <c r="C7" s="3">
+        <v>0.4</v>
       </c>
       <c r="D7" s="2">
         <v>0.2412</v>
@@ -608,8 +615,8 @@
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2">
-        <v>0.8</v>
+      <c r="C9" s="3">
+        <v>0.4</v>
       </c>
       <c r="D9" s="2">
         <v>0.2412</v>
@@ -648,8 +655,8 @@
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2">
-        <v>0.8</v>
+      <c r="C11" s="3">
+        <v>0.4</v>
       </c>
       <c r="D11" s="2">
         <v>0.2412</v>
@@ -688,8 +695,8 @@
       <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="2">
-        <v>0.8</v>
+      <c r="C13" s="3">
+        <v>0.4</v>
       </c>
       <c r="D13" s="2">
         <v>0.2412</v>
@@ -728,8 +735,8 @@
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2">
-        <v>0.8</v>
+      <c r="C15" s="3">
+        <v>0.4</v>
       </c>
       <c r="D15" s="2">
         <v>0.2412</v>
@@ -768,8 +775,8 @@
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="2">
-        <v>0.8</v>
+      <c r="C17" s="3">
+        <v>0.4</v>
       </c>
       <c r="D17" s="2">
         <v>0.2412</v>
